--- a/payment_forms/043_online_fine_payment_form--payment_forms.xlsx
+++ b/payment_forms/043_online_fine_payment_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -719,8 +719,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -748,12 +748,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'credit_card',_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'credit_card', 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'paypal',_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'paypal', 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'bank_transfer',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'bank_transfer', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'check',_'label':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'check', 'label': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'echeck',_'label':_'e-check'}</t>
+          <t>e-check</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'eCheck', 'label': 'E-Check'}</t>
+          <t>E-Check</t>
         </is>
       </c>
     </row>
